--- a/data/teotil3_modelled_loads_waterbodies.xlsx
+++ b/data/teotil3_modelled_loads_waterbodies.xlsx
@@ -2252,7 +2252,7 @@
         <v>291.010279738059</v>
       </c>
       <c r="H38" t="n">
-        <v>2.751801923157173</v>
+        <v>2.751799054411705</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2300,7 +2300,7 @@
         <v>329.5560684797675</v>
       </c>
       <c r="H39" t="n">
-        <v>2.584746197012764</v>
+        <v>2.584743328267296</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
         <v>245.9297001785788</v>
       </c>
       <c r="H40" t="n">
-        <v>2.584746197012764</v>
+        <v>2.584743328267296</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2396,7 +2396,7 @@
         <v>260.5201340956915</v>
       </c>
       <c r="H41" t="n">
-        <v>2.584746197012764</v>
+        <v>2.584743328267296</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -2444,7 +2444,7 @@
         <v>266.8726520640899</v>
       </c>
       <c r="H42" t="n">
-        <v>2.584746197012764</v>
+        <v>2.584743328267296</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
         <v>437.5403393586482</v>
       </c>
       <c r="H43" t="n">
-        <v>2.804317558927465</v>
+        <v>2.804314690181997</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>329.3458842933916</v>
       </c>
       <c r="H44" t="n">
-        <v>2.826059237355738</v>
+        <v>2.82605636861027</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2588,7 +2588,7 @@
         <v>345.7750622671535</v>
       </c>
       <c r="H45" t="n">
-        <v>2.844668934026209</v>
+        <v>2.844655755195272</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
         <v>324.8759985279742</v>
       </c>
       <c r="H46" t="n">
-        <v>3.024842175702581</v>
+        <v>3.024729737733456</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>326.0905374385456</v>
       </c>
       <c r="H47" t="n">
-        <v>2.821476185230491</v>
+        <v>2.821475842664924</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2732,7 +2732,7 @@
         <v>384.5432082494442</v>
       </c>
       <c r="H48" t="n">
-        <v>2.828521274168814</v>
+        <v>2.828517048347812</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2780,7 +2780,7 @@
         <v>337.8361641702253</v>
       </c>
       <c r="H49" t="n">
-        <v>2.82245505244574</v>
+        <v>2.822454170328228</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
         <v>16.94639200522369</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1754391234291628</v>
+        <v>0.1753528871040736</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -4604,7 +4604,7 @@
         <v>20.24938952567412</v>
       </c>
       <c r="H87" t="n">
-        <v>0.1742897835666108</v>
+        <v>0.1742035472415217</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
@@ -4652,7 +4652,7 @@
         <v>18.40061300152567</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1754759382455727</v>
+        <v>0.1753897019204835</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
         <v>15.67863345934943</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1766341932210185</v>
+        <v>0.1765479568959293</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>16.93446470808152</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1777600909365012</v>
+        <v>0.177673854611412</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
         <v>18.62833757442562</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1792430728764123</v>
+        <v>0.1791568365513231</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -4844,7 +4844,7 @@
         <v>17.2119227252676</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1817548807519169</v>
+        <v>0.1816686444268277</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -4892,7 +4892,7 @@
         <v>19.6713855171976</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1814194068499805</v>
+        <v>0.1810232427560225</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>16.25093293331816</v>
       </c>
       <c r="H94" t="n">
-        <v>0.2063560270495187</v>
+        <v>0.2029760697240703</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
@@ -4988,7 +4988,7 @@
         <v>14.09489922289445</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1782892284537857</v>
+        <v>0.1782789307135479</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         <v>14.14487151428741</v>
       </c>
       <c r="H96" t="n">
-        <v>0.1791997188159951</v>
+        <v>0.1790726879316629</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
@@ -5084,7 +5084,7 @@
         <v>12.62871836831382</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1782628637131518</v>
+        <v>0.1782363466960976</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
@@ -17284,7 +17284,7 @@
         <v>8.061719518962688</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7007216451871576</v>
+        <v>0.7007216451871577</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -18040,7 +18040,7 @@
         <v>0.3277588058391871</v>
       </c>
       <c r="J26" t="n">
-        <v>0.798138975398034</v>
+        <v>0.7981389753980338</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -18094,7 +18094,7 @@
         <v>0.3277588058391871</v>
       </c>
       <c r="J27" t="n">
-        <v>0.798138975398034</v>
+        <v>0.7981389753980338</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -18148,7 +18148,7 @@
         <v>0.3275811214494184</v>
       </c>
       <c r="J28" t="n">
-        <v>0.798138975398034</v>
+        <v>0.7981389753980338</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -18202,7 +18202,7 @@
         <v>0.3275811214494184</v>
       </c>
       <c r="J29" t="n">
-        <v>0.798138975398034</v>
+        <v>0.7981389753980338</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -18256,7 +18256,7 @@
         <v>0.3275811214494184</v>
       </c>
       <c r="J30" t="n">
-        <v>0.798138975398034</v>
+        <v>0.7981389753980338</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -18310,7 +18310,7 @@
         <v>0.3201023008762499</v>
       </c>
       <c r="J31" t="n">
-        <v>0.798138975398034</v>
+        <v>0.7981389753980338</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -18364,7 +18364,7 @@
         <v>0.2785805144758079</v>
       </c>
       <c r="J32" t="n">
-        <v>0.798138975398034</v>
+        <v>0.7981389753980338</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -18688,7 +18688,7 @@
         <v>2.431132957439861</v>
       </c>
       <c r="J38" t="n">
-        <v>0.005204542246169021</v>
+        <v>0.005201673500701477</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -18742,7 +18742,7 @@
         <v>2.431132957439861</v>
       </c>
       <c r="J39" t="n">
-        <v>0.005204542246169021</v>
+        <v>0.005201673500701477</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -18796,7 +18796,7 @@
         <v>2.431132957439861</v>
       </c>
       <c r="J40" t="n">
-        <v>0.005204542246169021</v>
+        <v>0.005201673500701477</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -18850,7 +18850,7 @@
         <v>2.431132957439861</v>
       </c>
       <c r="J41" t="n">
-        <v>0.005204542246169021</v>
+        <v>0.005201673500701477</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -18904,7 +18904,7 @@
         <v>2.431132957439861</v>
       </c>
       <c r="J42" t="n">
-        <v>0.005204542246169021</v>
+        <v>0.005201673500701477</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -18958,7 +18958,7 @@
         <v>2.431132957439861</v>
       </c>
       <c r="J43" t="n">
-        <v>0.005204542246169021</v>
+        <v>0.005201673500701477</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -19012,7 +19012,7 @@
         <v>2.431132957439861</v>
       </c>
       <c r="J44" t="n">
-        <v>0.005204542246169021</v>
+        <v>0.005201673500701477</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -19066,7 +19066,7 @@
         <v>2.431132957439861</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02390933010291518</v>
+        <v>0.02389615127197856</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -19120,7 +19120,7 @@
         <v>2.431132957439861</v>
       </c>
       <c r="J46" t="n">
-        <v>0.2039874805930123</v>
+        <v>0.2038750426238868</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -19174,7 +19174,7 @@
         <v>2.431132957439861</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0006214901209217811</v>
+        <v>0.0006211475553543999</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -19228,7 +19228,7 @@
         <v>2.431132957439861</v>
       </c>
       <c r="J48" t="n">
-        <v>0.007666579059244467</v>
+        <v>0.007662353238242828</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -19282,7 +19282,7 @@
         <v>2.431132957439861</v>
       </c>
       <c r="J49" t="n">
-        <v>0.00160035733617092</v>
+        <v>0.001599475218659438</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -19714,7 +19714,7 @@
         <v>0.7642835234332227</v>
       </c>
       <c r="J57" t="n">
-        <v>0.05736313125220042</v>
+        <v>0.05736313125220043</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -19930,7 +19930,7 @@
         <v>0.6208757863561346</v>
       </c>
       <c r="J61" t="n">
-        <v>0.2725773925636511</v>
+        <v>0.272577392563651</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -20416,7 +20416,7 @@
         <v>0.2380289953054925</v>
       </c>
       <c r="J70" t="n">
-        <v>0.403915361079481</v>
+        <v>0.4039153610794811</v>
       </c>
       <c r="K70" t="n">
         <v>0.0298018342725754</v>
@@ -20470,7 +20470,7 @@
         <v>0.2299113626763634</v>
       </c>
       <c r="J71" t="n">
-        <v>0.6951829923058113</v>
+        <v>0.6951829923058114</v>
       </c>
       <c r="K71" t="n">
         <v>0.0298018342725754</v>
@@ -20632,7 +20632,7 @@
         <v>0.0391675027592953</v>
       </c>
       <c r="J74" t="n">
-        <v>0.1197208463097051</v>
+        <v>0.1197208463097052</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -20686,7 +20686,7 @@
         <v>0.0391675027592953</v>
       </c>
       <c r="J75" t="n">
-        <v>0.1197208463097051</v>
+        <v>0.1197208463097052</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -20740,7 +20740,7 @@
         <v>0.0391675027592953</v>
       </c>
       <c r="J76" t="n">
-        <v>0.1197208463097051</v>
+        <v>0.1197208463097052</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -20794,7 +20794,7 @@
         <v>0.0391675027592953</v>
       </c>
       <c r="J77" t="n">
-        <v>0.1197208463097051</v>
+        <v>0.1197208463097052</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -20848,7 +20848,7 @@
         <v>0.0391675027592953</v>
       </c>
       <c r="J78" t="n">
-        <v>0.1197208463097051</v>
+        <v>0.1197208463097052</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
         <v>0.03790999841088518</v>
       </c>
       <c r="J79" t="n">
-        <v>0.1197208463097051</v>
+        <v>0.1197208463097052</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -20956,7 +20956,7 @@
         <v>0.0319678597434991</v>
       </c>
       <c r="J80" t="n">
-        <v>0.1197208463097051</v>
+        <v>0.1197208463097052</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -21064,7 +21064,7 @@
         <v>0.03156679792958678</v>
       </c>
       <c r="J82" t="n">
-        <v>0.1833815822813753</v>
+        <v>0.1833815822813754</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -21172,7 +21172,7 @@
         <v>0.03189236468681562</v>
       </c>
       <c r="J84" t="n">
-        <v>0.1280031281443735</v>
+        <v>0.1280031281443736</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -21280,7 +21280,7 @@
         <v>0.173283518957963</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0006726225312886932</v>
+        <v>0.0005863862061994982</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -21334,7 +21334,7 @@
         <v>0.173283518957963</v>
       </c>
       <c r="J87" t="n">
-        <v>0.0006726225312886932</v>
+        <v>0.0005863862061994982</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -21388,7 +21388,7 @@
         <v>0.173283518957963</v>
       </c>
       <c r="J88" t="n">
-        <v>0.0006726225312886932</v>
+        <v>0.0005863862061994982</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -21442,7 +21442,7 @@
         <v>0.173283518957963</v>
       </c>
       <c r="J89" t="n">
-        <v>0.0006726225312886932</v>
+        <v>0.0005863862061994982</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -21496,7 +21496,7 @@
         <v>0.173283518957963</v>
       </c>
       <c r="J90" t="n">
-        <v>0.0006726225312886932</v>
+        <v>0.0005863862061994982</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -21550,7 +21550,7 @@
         <v>0.173283518957963</v>
       </c>
       <c r="J91" t="n">
-        <v>0.0006726225312886932</v>
+        <v>0.0005863862061994982</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -21604,7 +21604,7 @@
         <v>0.173283518957963</v>
       </c>
       <c r="J92" t="n">
-        <v>0.0006726225312886932</v>
+        <v>0.0005863862061994982</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -21658,7 +21658,7 @@
         <v>0.173283518957963</v>
       </c>
       <c r="J93" t="n">
-        <v>0.003089984358773804</v>
+        <v>0.002693820264815769</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -21712,7 +21712,7 @@
         <v>0.173283518957963</v>
       </c>
       <c r="J94" t="n">
-        <v>0.02636285172796332</v>
+        <v>0.02298289440251488</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -21766,7 +21766,7 @@
         <v>0.173283518957963</v>
       </c>
       <c r="J95" t="n">
-        <v>8.031988953745703e-05</v>
+        <v>7.002214929968984e-05</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -21820,7 +21820,7 @@
         <v>0.173283518957963</v>
       </c>
       <c r="J96" t="n">
-        <v>0.0009908102517468607</v>
+        <v>0.0008637793674146852</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -21874,7 +21874,7 @@
         <v>0.173283518957963</v>
       </c>
       <c r="J97" t="n">
-        <v>0.0002068263358250307</v>
+        <v>0.0001803093187708413</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -28300,7 +28300,7 @@
         <v>0.4996733872253688</v>
       </c>
       <c r="J216" t="n">
-        <v>0.1847253039545046</v>
+        <v>0.1847253039545047</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -28408,7 +28408,7 @@
         <v>3.141509781129963</v>
       </c>
       <c r="J218" t="n">
-        <v>0.0006872876688545797</v>
+        <v>0.0006872876688545795</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -28462,7 +28462,7 @@
         <v>3.141509781129963</v>
       </c>
       <c r="J219" t="n">
-        <v>0.0006872876688545797</v>
+        <v>0.0006872876688545795</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -28516,7 +28516,7 @@
         <v>3.141509781129963</v>
       </c>
       <c r="J220" t="n">
-        <v>0.0006872876688545797</v>
+        <v>0.0006872876688545795</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -28570,7 +28570,7 @@
         <v>3.141509781129963</v>
       </c>
       <c r="J221" t="n">
-        <v>0.0006872876688545797</v>
+        <v>0.0006872876688545795</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -28624,7 +28624,7 @@
         <v>3.141509781129963</v>
       </c>
       <c r="J222" t="n">
-        <v>0.0006872876688545797</v>
+        <v>0.0006872876688545795</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -28678,7 +28678,7 @@
         <v>3.141509781129963</v>
       </c>
       <c r="J223" t="n">
-        <v>0.0006872876688545797</v>
+        <v>0.0006872876688545795</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
@@ -28732,7 +28732,7 @@
         <v>3.141509781129963</v>
       </c>
       <c r="J224" t="n">
-        <v>0.0006872876688545797</v>
+        <v>0.0006872876688545795</v>
       </c>
       <c r="K224" t="n">
         <v>0</v>
@@ -29002,7 +29002,7 @@
         <v>3.141509781129963</v>
       </c>
       <c r="J229" t="n">
-        <v>0.0002339558067535711</v>
+        <v>0.000233955806753571</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -29650,7 +29650,7 @@
         <v>0.07732897410676226</v>
       </c>
       <c r="J241" t="n">
-        <v>1.275335208808354e-05</v>
+        <v>1.275335208808351e-05</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -30190,7 +30190,7 @@
         <v>0.04878730336362866</v>
       </c>
       <c r="J251" t="n">
-        <v>0.005388085708142231</v>
+        <v>0.005388085708142232</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
@@ -30352,7 +30352,7 @@
         <v>0.3928185642275827</v>
       </c>
       <c r="J254" t="n">
-        <v>0.0001030931503281869</v>
+        <v>0.0001030931503281867</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
@@ -30406,7 +30406,7 @@
         <v>0.3928185642275827</v>
       </c>
       <c r="J255" t="n">
-        <v>0.0001030931503281869</v>
+        <v>0.0001030931503281867</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
@@ -30460,7 +30460,7 @@
         <v>0.3928185642275827</v>
       </c>
       <c r="J256" t="n">
-        <v>0.0001030931503281869</v>
+        <v>0.0001030931503281867</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -30514,7 +30514,7 @@
         <v>0.3928185642275827</v>
       </c>
       <c r="J257" t="n">
-        <v>0.0001030931503281869</v>
+        <v>0.0001030931503281867</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
@@ -30568,7 +30568,7 @@
         <v>0.3928185642275827</v>
       </c>
       <c r="J258" t="n">
-        <v>0.0001030931503281869</v>
+        <v>0.0001030931503281867</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -30622,7 +30622,7 @@
         <v>0.3928185642275827</v>
       </c>
       <c r="J259" t="n">
-        <v>0.0001030931503281869</v>
+        <v>0.0001030931503281867</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -30676,7 +30676,7 @@
         <v>0.3928185642275827</v>
       </c>
       <c r="J260" t="n">
-        <v>0.0001030931503281869</v>
+        <v>0.0001030931503281867</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -30730,7 +30730,7 @@
         <v>0.3928185642275827</v>
       </c>
       <c r="J261" t="n">
-        <v>0.0001052801130391069</v>
+        <v>0.0001052801130391068</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
